--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_metals_mining.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,26 +587,23 @@
           <t>Metals &amp; Mining</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.492</v>
-      </c>
       <c r="G2">
-        <v>-0.07577586206896551</v>
+        <v>0.09862778730703257</v>
       </c>
       <c r="H2">
-        <v>-0.07577586206896551</v>
+        <v>0.09862778730703257</v>
       </c>
       <c r="I2">
-        <v>-0.09241379310344829</v>
+        <v>-0.7084048027444254</v>
       </c>
       <c r="J2">
-        <v>-0.09241379310344829</v>
+        <v>-0.7084048027444254</v>
       </c>
       <c r="K2">
-        <v>-3.11</v>
+        <v>-3.55</v>
       </c>
       <c r="L2">
-        <v>-0.2681034482758621</v>
+        <v>-0.6089193825042881</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,67 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.666</v>
+        <v>0.024</v>
       </c>
       <c r="V2">
-        <v>0.01807670385147789</v>
+        <v>0.0008571428571428572</v>
       </c>
       <c r="W2">
-        <v>0.002133249921801694</v>
+        <v>-0.3446601941747572</v>
       </c>
       <c r="X2">
-        <v>0.5781818597833821</v>
+        <v>0.1339085906897823</v>
       </c>
       <c r="Y2">
-        <v>-0.5760486098615805</v>
+        <v>-0.4785687848645395</v>
       </c>
       <c r="Z2">
-        <v>0.5330637378796931</v>
+        <v>0.2285288698992591</v>
+      </c>
+      <c r="AA2">
+        <v>-0.1618909490023911</v>
       </c>
       <c r="AB2">
-        <v>0.1450919707605185</v>
+        <v>0.1131729244169428</v>
+      </c>
+      <c r="AC2">
+        <v>-0.2750638734193339</v>
       </c>
       <c r="AD2">
-        <v>22.28</v>
+        <v>10.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>22.28</v>
+        <v>10.8</v>
       </c>
       <c r="AG2">
-        <v>21.614</v>
+        <v>10.776</v>
       </c>
       <c r="AH2">
-        <v>0.3768414999238875</v>
+        <v>0.2783505154639176</v>
       </c>
       <c r="AI2">
-        <v>0.8795894196604818</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="AJ2">
-        <v>0.369741861539251</v>
+        <v>0.2779038580565298</v>
       </c>
       <c r="AK2">
-        <v>0.8763379824845929</v>
+        <v>0.4085532302092812</v>
       </c>
       <c r="AL2">
-        <v>1.065</v>
+        <v>0.272</v>
       </c>
       <c r="AM2">
-        <v>0.964</v>
+        <v>0.215</v>
       </c>
       <c r="AN2">
-        <v>-81.61172161172161</v>
+        <v>-3.564356435643565</v>
       </c>
       <c r="AO2">
-        <v>-1.006572769953052</v>
+        <v>-15.18382352941176</v>
       </c>
       <c r="AP2">
-        <v>-79.17216117216117</v>
+        <v>-3.556435643564357</v>
       </c>
       <c r="AQ2">
-        <v>-1.112033195020747</v>
+        <v>-19.20930232558139</v>
       </c>
     </row>
     <row r="3">
@@ -709,26 +712,23 @@
           <t>Metals &amp; Mining</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.492</v>
-      </c>
       <c r="G3">
-        <v>-0.0481896551724138</v>
+        <v>0.09862778730703257</v>
       </c>
       <c r="H3">
-        <v>-0.0481896551724138</v>
+        <v>0.09862778730703257</v>
       </c>
       <c r="I3">
-        <v>-0.02620689655172414</v>
+        <v>-0.7084048027444254</v>
       </c>
       <c r="J3">
-        <v>-0.02620689655172414</v>
+        <v>-0.7084048027444254</v>
       </c>
       <c r="K3">
-        <v>-1.92</v>
+        <v>-3.55</v>
       </c>
       <c r="L3">
-        <v>-0.1655172413793103</v>
+        <v>-0.6089193825042881</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,174 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.659</v>
+        <v>0.024</v>
       </c>
       <c r="V3">
-        <v>0.01820441988950276</v>
+        <v>0.0008571428571428572</v>
       </c>
       <c r="W3">
-        <v>-0.1669565217391304</v>
+        <v>-0.3446601941747572</v>
       </c>
       <c r="X3">
-        <v>0.1767447548375768</v>
+        <v>0.1339085906897823</v>
       </c>
       <c r="Y3">
-        <v>-0.3437012765767072</v>
+        <v>-0.4785687848645395</v>
       </c>
       <c r="Z3">
-        <v>0.5330637378796931</v>
+        <v>0.2285288698992591</v>
       </c>
       <c r="AA3">
-        <v>-0.01396994623408851</v>
+        <v>-0.1618909490023911</v>
       </c>
       <c r="AB3">
-        <v>0.1431463544286137</v>
+        <v>0.1131729244169428</v>
       </c>
       <c r="AC3">
-        <v>-0.1571163006627022</v>
+        <v>-0.2750638734193339</v>
       </c>
       <c r="AD3">
-        <v>15.7</v>
+        <v>10.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.7</v>
+        <v>10.8</v>
       </c>
       <c r="AG3">
-        <v>15.041</v>
+        <v>10.776</v>
       </c>
       <c r="AH3">
-        <v>0.302504816955684</v>
+        <v>0.2783505154639176</v>
       </c>
       <c r="AI3">
-        <v>0.6061776061776062</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="AJ3">
-        <v>0.2935344743467145</v>
+        <v>0.2779038580565298</v>
       </c>
       <c r="AK3">
-        <v>0.5958955667366586</v>
+        <v>0.4085532302092812</v>
       </c>
       <c r="AL3">
-        <v>0.741</v>
+        <v>0.272</v>
       </c>
       <c r="AM3">
-        <v>0.646</v>
+        <v>0.215</v>
       </c>
       <c r="AN3">
-        <v>31.78137651821862</v>
+        <v>-3.564356435643565</v>
       </c>
       <c r="AO3">
-        <v>-0.4102564102564102</v>
+        <v>-15.18382352941176</v>
       </c>
       <c r="AP3">
-        <v>30.44736842105263</v>
+        <v>-3.556435643564357</v>
       </c>
       <c r="AQ3">
-        <v>-0.4705882352941176</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Kazakhstan</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Joint Stock Company Subsidiary Company Aktobe Temir-VS (KAS:ATVS)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Metals &amp; Mining</t>
-        </is>
-      </c>
-      <c r="K4">
-        <v>-1.19</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0.007</v>
-      </c>
-      <c r="V4">
-        <v>0.01088646967340591</v>
-      </c>
-      <c r="W4">
-        <v>0.1712230215827338</v>
-      </c>
-      <c r="X4">
-        <v>0.9796189647291875</v>
-      </c>
-      <c r="Y4">
-        <v>-0.8083959431464537</v>
-      </c>
-      <c r="AB4">
-        <v>0.1470375870924233</v>
-      </c>
-      <c r="AD4">
-        <v>6.58</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>6.58</v>
-      </c>
-      <c r="AG4">
-        <v>6.573</v>
-      </c>
-      <c r="AH4">
-        <v>0.9109788176657899</v>
-      </c>
-      <c r="AI4">
-        <v>-11.5438596491228</v>
-      </c>
-      <c r="AJ4">
-        <v>0.9108924611973392</v>
-      </c>
-      <c r="AK4">
-        <v>-11.39168110918544</v>
-      </c>
-      <c r="AL4">
-        <v>0.324</v>
-      </c>
-      <c r="AM4">
-        <v>0.318</v>
-      </c>
-      <c r="AN4">
-        <v>-8.578878748370274</v>
-      </c>
-      <c r="AO4">
-        <v>-2.37037037037037</v>
-      </c>
-      <c r="AP4">
-        <v>-8.569752281616688</v>
-      </c>
-      <c r="AQ4">
-        <v>-2.415094339622641</v>
+        <v>-19.20930232558139</v>
       </c>
     </row>
   </sheetData>
